--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774647</v>
+        <v>121774670</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,32 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689312</v>
+        <v>689340</v>
       </c>
       <c r="R3" t="n">
-        <v>6605102</v>
+        <v>6605110</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +934,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R4" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774685</v>
+        <v>121774647</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,27 +1051,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R5" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774738</v>
+        <v>121774685</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774670</v>
+        <v>121774647</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +808,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689340</v>
+        <v>689312</v>
       </c>
       <c r="R3" t="n">
-        <v>6605110</v>
+        <v>6605102</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,27 +930,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R4" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774647</v>
+        <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,36 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R5" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R2" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774647</v>
+        <v>121774685</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,32 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R3" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774670</v>
+        <v>121774738</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +930,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R4" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774738</v>
+        <v>121774647</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1047,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R5" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774685</v>
+        <v>121774647</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,27 +817,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R3" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -881,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1035,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774647</v>
+        <v>121774685</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,32 +1056,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R5" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774670</v>
+        <v>121774647</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689340</v>
+        <v>689312</v>
       </c>
       <c r="R2" t="n">
-        <v>6605110</v>
+        <v>6605102</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774647</v>
+        <v>121774685</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,32 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R3" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -886,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,27 +1047,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R5" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774738</v>
+        <v>121774670</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +926,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R4" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774670</v>
+        <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,35 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R5" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774647</v>
+        <v>121774670</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>97085</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689312</v>
+        <v>689340</v>
       </c>
       <c r="R2" t="n">
-        <v>6605102</v>
+        <v>6605110</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774685</v>
+        <v>121774647</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>56577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,27 +817,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R3" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +939,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R4" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,7 +1043,7 @@
         <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B2" t="n">
-        <v>97085</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R2" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774685</v>
+        <v>121774738</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>57381</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774738</v>
+        <v>121774670</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>97087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1043,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R5" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>97094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R2" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774738</v>
+        <v>121774685</v>
       </c>
       <c r="B4" t="n">
-        <v>57381</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774670</v>
+        <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>97087</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,35 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R5" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B2" t="n">
-        <v>97094</v>
+        <v>8425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R2" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,7 +795,7 @@
         <v>121774647</v>
       </c>
       <c r="B3" t="n">
-        <v>56577</v>
+        <v>56581</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>97103</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,27 +930,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -968,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R4" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,7 +1043,7 @@
         <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774685</v>
+        <v>121774647</v>
       </c>
       <c r="B2" t="n">
-        <v>8425</v>
+        <v>56582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R2" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +770,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774647</v>
+        <v>121774685</v>
       </c>
       <c r="B3" t="n">
-        <v>56581</v>
+        <v>8425</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,32 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R3" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774670</v>
+        <v>121774738</v>
       </c>
       <c r="B4" t="n">
-        <v>97103</v>
+        <v>57388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R4" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774738</v>
+        <v>121774670</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>97111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1043,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R5" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774685</v>
+        <v>121774738</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>57388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774738</v>
+        <v>121774685</v>
       </c>
       <c r="B4" t="n">
-        <v>57388</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,31 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774647</v>
+        <v>121774738</v>
       </c>
       <c r="B2" t="n">
-        <v>56582</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689312</v>
+        <v>689352</v>
       </c>
       <c r="R2" t="n">
-        <v>6605102</v>
+        <v>6605076</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121774738</v>
+        <v>121774647</v>
       </c>
       <c r="B3" t="n">
-        <v>57388</v>
+        <v>56584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +804,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689352</v>
+        <v>689312</v>
       </c>
       <c r="R3" t="n">
-        <v>6605076</v>
+        <v>6605102</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774685</v>
+        <v>121774670</v>
       </c>
       <c r="B4" t="n">
-        <v>8425</v>
+        <v>97113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,27 +930,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,13 +963,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R4" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B5" t="n">
-        <v>97111</v>
+        <v>8425</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,31 +1056,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R5" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121774738</v>
+        <v>121774670</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>97113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689352</v>
+        <v>689340</v>
       </c>
       <c r="R2" t="n">
-        <v>6605076</v>
+        <v>6605110</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -914,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121774670</v>
+        <v>121774685</v>
       </c>
       <c r="B4" t="n">
-        <v>97113</v>
+        <v>8425</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,31 +939,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,13 +968,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689340</v>
+        <v>689352</v>
       </c>
       <c r="R4" t="n">
-        <v>6605110</v>
+        <v>6605076</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121774685</v>
+        <v>121774738</v>
       </c>
       <c r="B5" t="n">
-        <v>8425</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,31 +1052,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,118 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123756048</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97350</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Syd om Bromsebyvägen, Syd om Bromsebyvägen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>689517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6605026</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>123756048</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>123756048</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 68109-2019 artfynd.xlsx
+++ b/artfynd/A 68109-2019 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>123756048</v>
       </c>
       <c r="B6" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
